--- a/examples/excel/charts/charts-basic.xlsx
+++ b/examples/excel/charts/charts-basic.xlsx
@@ -3,13 +3,13 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Column Charts" sheetId="2" r:id="R560a4bf398d94f01"/>
-    <x:sheet name="2-Bar Charts" sheetId="3" r:id="Ra307cbd6b4f4441c"/>
-    <x:sheet name="3-Line Charts" sheetId="4" r:id="Re3598e0b3cdf47fa"/>
-    <x:sheet name="4-Area Charts" sheetId="5" r:id="Rc8e69b068a2c46d3"/>
-    <x:sheet name="5-Styling" sheetId="6" r:id="Rfb14b7252fc84210"/>
-    <x:sheet name="6-Layout" sheetId="7" r:id="Rd437f303bdbc441e"/>
-    <x:sheet name="7-Effects" sheetId="8" r:id="R0837b779f65a41f0"/>
+    <x:sheet name="1-Column Charts" sheetId="2" r:id="R3196f9782d8045ab"/>
+    <x:sheet name="2-Bar Charts" sheetId="3" r:id="Rf52db2e2f9484030"/>
+    <x:sheet name="3-Line Charts" sheetId="4" r:id="Re73d28b731e94949"/>
+    <x:sheet name="4-Area Charts" sheetId="5" r:id="R21307deedebb42c3"/>
+    <x:sheet name="5-Styling" sheetId="6" r:id="Rcf8703d723724acd"/>
+    <x:sheet name="6-Layout" sheetId="7" r:id="Rfa293ee8336342be"/>
+    <x:sheet name="7-Effects" sheetId="8" r:id="R66aa36891c724015"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -644,10 +644,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0070C0"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -754,10 +755,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="00B050"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -864,10 +866,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -974,10 +977,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="31750">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
             <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:outerShdw blurRad="50800" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
@@ -1077,7 +1081,6 @@
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:marker val="1"/>
         <c:smooth val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -1157,9 +1160,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1258,9 +1263,11 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1359,9 +1366,11 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A5A5A5"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1460,9 +1469,11 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -1554,7 +1565,6 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -1670,10 +1680,10 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
@@ -1774,10 +1784,10 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
@@ -1878,10 +1888,10 @@
             <c:v>North</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="A5A5A5"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
@@ -1982,10 +1992,10 @@
             <c:v>West</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
               <a:prstDash val="sysDash"/>
             </a:ln>
           </c:spPr>
@@ -2079,7 +2089,6 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -3654,7 +3663,7 @@
     </c:view3D>
     <c:plotArea>
       <c:layout/>
-      <c:areaChart>
+      <c:area3DChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -4063,7 +4072,8 @@
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
-      </c:areaChart>
+        <c:axId val="3"/>
+      </c:area3DChart>
       <c:catAx>
         <c:axId val="1"/>
         <c:scaling>
@@ -4096,6 +4106,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -4118,10 +4137,23 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1400" b="1"/>
+              <a:defRPr sz="1800" b="1"/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:rPr lang="en-US" sz="1800" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F4E79"/>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="38100" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
+                    <a:srgbClr val="000000">
+                      <a:alpha val="30000"/>
+                    </a:srgbClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="Georgia"/>
+                <a:ea typeface="Georgia"/>
+              </a:rPr>
               <a:t>Fully Styled Chart</a:t>
             </a:r>
           </a:p>
@@ -4598,15 +4630,21 @@
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
-            <c:v>1</c:v>
+            <c:v>Ref (160)</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:srgbClr val="FFFFFF"/>
               </a:solidFill>
-              <a:prstDash val="sysDash"/>
             </a:ln>
+            <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:outerShdw blurRad="38100" dist="25400" dir="18900000" algn="tl" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="25000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -4990,7 +5028,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -5042,6 +5080,7 @@
               <a:srgbClr val="4472C4"/>
             </a:solidFill>
           </c:spPr>
+          <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strLit>
               <c:ptCount val="4"/>
@@ -5077,7 +5116,6 @@
               </c:pt>
             </c:numLit>
           </c:val>
-          <c:invertIfNegative val="1"/>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="outEnd"/>
@@ -5674,10 +5712,11 @@
             <c:v>Revenue</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
@@ -5688,6 +5727,31 @@
               </a:solidFill>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                  <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                  <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>Peak!</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+            </c:dLbl>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strLit>
               <c:ptCount val="4"/>
@@ -5812,10 +5876,28 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3"/>
+          <c:y val="0.01"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
     </c:title>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15"/>
+          <c:y val="0.15"/>
+          <c:w val="0.7"/>
+          <c:h val="0.7"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -6061,6 +6143,14 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.02"/>
+          <c:y val="0.4"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="1"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -6166,8 +6256,8 @@
       <c:valAx>
         <c:axId val="2"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="maxMin"/>
-          <c:logBase val="10"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -6233,6 +6323,35 @@
               <a:srgbClr val="4472C4"/>
             </a:solidFill>
           </c:spPr>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                  <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                  <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>Best!</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strLit>
               <c:ptCount val="4"/>
@@ -6371,11 +6490,11 @@
             <c:v>Measurement</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="80000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="square"/>
@@ -6386,6 +6505,11 @@
               </a:solidFill>
             </c:spPr>
           </c:marker>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="both"/>
+            <c:errValType val="percentage"/>
+          </c:errBars>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -6427,11 +6551,6 @@
               </c:pt>
             </c:numLit>
           </c:val>
-          <c:errBars>
-            <c:errDir val="y"/>
-            <c:errBarType val="both"/>
-            <c:errValType val="fixedVal"/>
-          </c:errBars>
         </c:ser>
         <c:marker val="1"/>
         <c:axId val="1"/>
@@ -6662,10 +6781,18 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1400" b="1"/>
+              <a:defRPr sz="1600" b="1"/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:rPr lang="en-US" sz="1600" b="1">
+                <a:effectLst>
+                  <a:glow rad="101600">
+                    <a:srgbClr val="4472C4">
+                      <a:alpha val="60000"/>
+                    </a:srgbClr>
+                  </a:glow>
+                </a:effectLst>
+              </a:rPr>
               <a:t>Glow Title + Area Fill</a:t>
             </a:r>
           </a:p>
@@ -6685,11 +6812,17 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:gradFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:srgbClr val="4472C4"/>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:srgbClr val="BDD7EE"/>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="1"/>
+            </a:gradFill>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -6788,11 +6921,17 @@
             <c:v>South</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31">
-                <a:alpha val="70000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:gradFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:srgbClr val="4472C4"/>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:srgbClr val="BDD7EE"/>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="1"/>
+            </a:gradFill>
           </c:spPr>
           <c:cat>
             <c:strRef>
@@ -8113,10 +8252,16 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1400" b="1"/>
+              <a:defRPr sz="1600" b="1"/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:rPr lang="en-US" sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F4E79"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:rPr>
               <a:t>3D Regional Sales</a:t>
             </a:r>
           </a:p>
@@ -8522,6 +8667,7 @@
         <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
+        <c:axId val="3"/>
       </c:bar3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -8555,6 +8701,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -9959,6 +10114,7 @@
         <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
+        <c:axId val="3"/>
       </c:bar3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -9992,6 +10148,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -10041,9 +10206,11 @@
             <c:v>East</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -10057,11 +10224,90 @@
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>198</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -10157,7 +10403,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24718cc0980d4fc4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R72db84ddb0fd49e5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10187,7 +10433,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26bebb52a8c84a5b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R174634a7b7a6462a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10217,7 +10463,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R432dd9cf996a4477"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcf095a1a6b4e4158"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10247,7 +10493,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7764e1f6101d4a04"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf91a020e9544456e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10282,7 +10528,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R247838841eb243ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4964dda0072c4742"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10312,7 +10558,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re2d1bdff31e14704"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R586eef07b7644016"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10342,7 +10588,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R00480fe234004afe"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R00816547d68e4f83"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10372,7 +10618,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rddcf743be72448c7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0fa8464ee5ab4741"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10407,7 +10653,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R21f3bd03a26f456b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R133c7082d22c4c66"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10437,7 +10683,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a3080d6813d4c03"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1384f73ffb4748b3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10467,7 +10713,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7e8ef4350d474a4b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R77c909a784c246be"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10497,7 +10743,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R65048789872c451f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R352c164e1f5349cb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10532,7 +10778,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R458a7b96f2894d9c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra390c8929ae849de"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10562,7 +10808,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R08349980ebf04e90"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd8005db01f64caf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10592,7 +10838,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R93598b57b04b4af7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re43780f416ca44cc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10622,7 +10868,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R25023aaf1f3c4bd3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R05e4bb4c04a5483d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10657,7 +10903,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbf4413b997034260"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdc7fc52f368b4b4d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10687,7 +10933,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbbeb739ec15a4f06"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R48f24dbfa1f54e9c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10717,7 +10963,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab6081858cac4d3c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4921dffa2ed84fcf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10747,7 +10993,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re0f15ccdde594f94"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rabc8ac748c594bc4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10782,7 +11028,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R729d8afe59bb4881"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R19ead485043743d3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10812,7 +11058,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7347994c558345fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra3f6c61b4b9a407b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10842,7 +11088,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R667668fa10bf47d8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4acb947ad6f84079"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10872,7 +11118,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R52c96cea30594025"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9d58d8c39c59499e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10907,7 +11153,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1d9756de84e41f6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra139210be86348b8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10937,7 +11183,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5a8b6d30e71e4327"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3348d8e2e6644656"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10967,7 +11213,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2b5f4a480d184b1c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4ce24b42e80a4bd7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10997,13 +11243,122 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R60655219932349b6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R61d2a113210b4ee7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11237,48 +11592,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15e25689d885457f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bd94a6f9fb44748"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e9f1930d6b942a5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91d9764aec664274"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1752ad416534669"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d436a5be35f40a1"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a796ab3d4104728"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22e60db8db2a4a31"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c4c2c9aed3e49ec"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3559848fe51f4483"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dbedbcc516f4826"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R331a11c1ef68439a"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdfab560920e4fe7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc00c81af2a4d4592"/>
 </x:worksheet>
 </file>